--- a/events/Kasai_2021_OG/Kasai_2021_OG_start.xlsx
+++ b/events/Kasai_2021_OG/Kasai_2021_OG_start.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ROC</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ROC</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ROC</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>ROC</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>ROC</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J161" t="n">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>ROC</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J183" t="n">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>ROC</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J207" t="n">
@@ -13797,7 +13797,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>ROC</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J229" t="n">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>ROC</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J246" t="n">
@@ -16843,7 +16843,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>ROC</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J281" t="n">
